--- a/tools/importer/reports/import-story-category.report.xlsx
+++ b/tools/importer/reports/import-story-category.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="669">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,9 +19,18 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
+    <t>sections</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
@@ -37,6 +46,57 @@
     <t>url</t>
   </si>
   <si>
+    <t>us/en/all-stories.report.json</t>
+  </si>
+  <si>
+    <t>["cards-stories","cards-stories"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>us/en/all-stories</t>
+  </si>
+  <si>
+    <t>[{"id":"hero-heading","style":"arc"},{"id":"story-cards","style":null}]</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>story-category</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:52:24.359Z</t>
+  </si>
+  <si>
+    <t>All Stories | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/all-stories.html</t>
+  </si>
+  <si>
+    <t>us/en/newsroom.report.json</t>
+  </si>
+  <si>
+    <t>["hero-featured","cards-stories","contact-card"]</t>
+  </si>
+  <si>
+    <t>us/en/newsroom</t>
+  </si>
+  <si>
+    <t>topic-hub</t>
+  </si>
+  <si>
+    <t>2026-03-10T18:30:14.843Z</t>
+  </si>
+  <si>
+    <t>Newsroom | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/newsroom.html</t>
+  </si>
+  <si>
     <t>us/en/our-company.report.json</t>
   </si>
   <si>
@@ -46,13 +106,10 @@
     <t>us/en/our-company</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>company-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:15.426Z</t>
+    <t>2026-03-06T14:59:38.007Z</t>
   </si>
   <si>
     <t>Our Company | About UPS</t>
@@ -73,7 +130,7 @@
     <t>story-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:39:42.372Z</t>
+    <t>2026-03-06T14:59:29.310Z</t>
   </si>
   <si>
     <t>Our Stories | About UPS</t>
@@ -82,6 +139,66 @@
     <t>https://about.ups.com/us/en/our-stories.html</t>
   </si>
   <si>
+    <t>us/en/newsroom/awards-and-recognition.report.json</t>
+  </si>
+  <si>
+    <t>["cards-awards"]</t>
+  </si>
+  <si>
+    <t>us/en/newsroom/awards-and-recognition</t>
+  </si>
+  <si>
+    <t>universal</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:41:10.382Z</t>
+  </si>
+  <si>
+    <t>Awards and Recognition | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/newsroom/awards-and-recognition.html</t>
+  </si>
+  <si>
+    <t>us/en/newsroom/facebook-rules.report.json</t>
+  </si>
+  <si>
+    <t>["article-header","embed","social-share","cards-stories"]</t>
+  </si>
+  <si>
+    <t>us/en/newsroom/facebook-rules</t>
+  </si>
+  <si>
+    <t>story-article</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:20.982Z</t>
+  </si>
+  <si>
+    <t>Facebook Rules</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/newsroom/facebook-rules.html</t>
+  </si>
+  <si>
+    <t>us/en/our-company/great-employer.report.json</t>
+  </si>
+  <si>
+    <t>["hero-featured","columns-feature","fact-sheets","fact-sheets","fact-sheets","fact-sheets","cards-stories","cards-stories","cards-stories","cards-stories"]</t>
+  </si>
+  <si>
+    <t>us/en/our-company/great-employer</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:40:22.036Z</t>
+  </si>
+  <si>
+    <t>Great Employer</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-company/great-employer.html</t>
+  </si>
+  <si>
     <t>us/en/our-company/our-culture.report.json</t>
   </si>
   <si>
@@ -94,7 +211,7 @@
     <t>company-culture</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:19.704Z</t>
+    <t>2026-03-06T14:40:11.991Z</t>
   </si>
   <si>
     <t>Our Culture</t>
@@ -106,16 +223,13 @@
     <t>us/en/our-company/our-strategy.report.json</t>
   </si>
   <si>
-    <t>["hero-featured","cards-stories","cards-stories","columns-feature"]</t>
+    <t>["hero-featured","cards-stories","columns-feature"]</t>
   </si>
   <si>
     <t>us/en/our-company/our-strategy</t>
   </si>
   <si>
-    <t>company-strategy</t>
-  </si>
-  <si>
-    <t>2026-03-06T14:21:12.153Z</t>
+    <t>2026-03-11T11:04:31.187Z</t>
   </si>
   <si>
     <t>Our Strategy | About UPS</t>
@@ -124,18 +238,88 @@
     <t>https://about.ups.com/us/en/our-company/our-strategy.html</t>
   </si>
   <si>
+    <t>us/en/our-company/suppliers.report.json</t>
+  </si>
+  <si>
+    <t>["hero-featured"]</t>
+  </si>
+  <si>
+    <t>us/en/our-company/suppliers</t>
+  </si>
+  <si>
+    <t>2026-03-10T19:58:53.741Z</t>
+  </si>
+  <si>
+    <t>Suppliers | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-company/suppliers.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/community.report.json</t>
+  </si>
+  <si>
+    <t>["hero-featured","hero-featured","columns-feature","columns-feature","fact-sheets","cards-stories"]</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/community</t>
+  </si>
+  <si>
+    <t>2026-03-10T17:40:17.012Z</t>
+  </si>
+  <si>
+    <t>Community | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-impact/community.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability.html.report.json</t>
+  </si>
+  <si>
+    <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
+    at processUrl (file:///home/node/.claude/plugins/cache/excat-marketplace/excat/2.1.1/skills/excat-content-import/scripts/run-bulk-import.js:293:13)
+    at runNextTicks (node:internal/process/task_queues:65:5)
+    at process.processImmediate (node:internal/timers:472:9)
+    at async main (file:///home/node/.claude/plugins/cache/excat-marketplace/excat/2.1.1/skills/excat-content-import/scripts/run-bulk-import.js:457:22)</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:24:47.678Z</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-impact/sustainability.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero-featured","hero-featured","cards-stories","fact-sheets"]</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:25:31.357Z</t>
+  </si>
+  <si>
+    <t>Sustainability | About UPS</t>
+  </si>
+  <si>
     <t>us/en/our-stories/customer-first.report.json</t>
   </si>
   <si>
-    <t>["cards-stories","cards-stories"]</t>
-  </si>
-  <si>
     <t>us/en/our-stories/customer-first</t>
   </si>
   <si>
-    <t>story-category</t>
-  </si>
-  <si>
     <t>2026-03-06T14:39:45.703Z</t>
   </si>
   <si>
@@ -173,6 +357,1671 @@
   </si>
   <si>
     <t>https://about.ups.com/us/en/our-stories/people-led.html</t>
+  </si>
+  <si>
+    <t>us/en/our-company/governance/carbon-neutral-credentials.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-company/governance/carbon-neutral-credentials</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:25.074Z</t>
+  </si>
+  <si>
+    <t>Carbon Neutral Credentials | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-company/governance/carbon-neutral-credentials.html</t>
+  </si>
+  <si>
+    <t>us/en/our-company/governance/transparency-rule.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-company/governance/transparency-rule</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:32.168Z</t>
+  </si>
+  <si>
+    <t>Transparency Rule</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-company/governance/transparency-rule.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/community/the-ups-foundation-mission-and-purpose.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/community/the-ups-foundation-mission-and-purpose</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:40.596Z</t>
+  </si>
+  <si>
+    <t>The UPS Foundation Mission and Purpose | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-impact/community/the-ups-foundation-mission-and-purpose.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/reporting/gender-equality-index-ups-france.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/reporting/gender-equality-index-ups-france</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:49.770Z</t>
+  </si>
+  <si>
+    <t>Gender Equality Index – UPS France</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-impact/reporting/gender-equality-index---ups-france-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability/key-highlights-from-ups-s-latest-sustainability-and-community-im.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-impact/sustainability/key-highlights-from-ups-s-latest-sustainability-and-community-im</t>
+  </si>
+  <si>
+    <t>2026-03-11T12:51:58.081Z</t>
+  </si>
+  <si>
+    <t>Key highlights from UPS’s latest Sustainability and Community Impact Report</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-impact/sustainability/key-highlights-from-ups-s-latest-sustainability-and-community-im.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/3-reasons-you-can-trust-ups-to-ship-luxury-watches-around-the-wo.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/3-reasons-you-can-trust-ups-to-ship-luxury-watches-around-the-wo</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:19.477Z</t>
+  </si>
+  <si>
+    <t>3 reasons you can trust UPS to ship luxury watches around the world</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/3-reasons-you-can-trust-ups-to-ship-luxury-watches-around-the-wo.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/3-ways-ups-helps-businesses-navigate-global-trade-and-tariffs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/3-ways-ups-helps-businesses-navigate-global-trade-and-tariffs</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:25.633Z</t>
+  </si>
+  <si>
+    <t>3 ways UPS helps businesses navigate global trade and tariffs</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/3-ways-ups-helps-businesses-navigate-global-trade-and-tariffs.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/4-key-takeaways-from-ups-s-2025-impact-summit.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/4-key-takeaways-from-ups-s-2025-impact-summit</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:31.576Z</t>
+  </si>
+  <si>
+    <t>4 key takeaways from UPS’s 2025 Impact Summit</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/4-key-takeaways-from-ups-s-2025-impact-summit.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/4-things-you-need-to-know-from-ups-s-q2-2025-earnings-announceme.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/4-things-you-need-to-know-from-ups-s-q2-2025-earnings-announceme</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:38.093Z</t>
+  </si>
+  <si>
+    <t>4 things you need to know from UPS’s Q2 2025 earnings announcement</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/4-things-you-need-to-know-from-ups-s-q2-2025-earnings-announceme.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/5-things-every-business-should-know-about-returns-in-2025-and-be.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/5-things-every-business-should-know-about-returns-in-2025-and-be</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:43.116Z</t>
+  </si>
+  <si>
+    <t>Survey reveals: Easy returns can build customer loyalty</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/5-things-every-business-should-know-about-returns-in-2025-and-be.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/5-things-you-didn-t-know-the-ups-store-could-do-for-your-small-b.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/5-things-you-didn-t-know-the-ups-store-could-do-for-your-small-b</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:11:21.766Z</t>
+  </si>
+  <si>
+    <t>5 things you didn’t know The UPS Store could do for your small business</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/5-things-you-didn-t-know-the-ups-store-could-do-for-your-small-b.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/a-peek-into-peak-shipping-season-at-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/a-peek-into-peak-shipping-season-at-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:57.230Z</t>
+  </si>
+  <si>
+    <t>A peek into peak shipping season at UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/a-peek-into-peak-shipping-season-at-ups.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/beat-the-holiday-rush-shop-early-ship-early-with-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/beat-the-holiday-rush-shop-early-ship-early-with-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:02.686Z</t>
+  </si>
+  <si>
+    <t>Beat the holiday rush: shop early, ship early with UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/beat-the-holiday-rush--shop-early--ship-early-with-ups.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/college-student-essentials-shipped-by-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/college-student-essentials-shipped-by-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:48.501Z</t>
+  </si>
+  <si>
+    <t>👩‍🎓 College student essentials, shipped by UPS 👨‍🎓</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/_-college-student-essentials--shipped-by-ups-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/delivering-iconic-flavors-with-ups-the-recipe-behind-goldbelly.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/delivering-iconic-flavors-with-ups-the-recipe-behind-goldbelly</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:07.176Z</t>
+  </si>
+  <si>
+    <t>Delivering iconic flavors with UPS: the recipe behind Goldbelly’s shipping success</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/delivering-iconic-flavors-with-ups--the-recipe-behind-goldbelly-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/fresh-products-need-a-reliable-shipper.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/fresh-products-need-a-reliable-shipper</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:22.235Z</t>
+  </si>
+  <si>
+    <t>Fresh products need a reliable shipper</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/fresh-products-need-a-reliable-shipper.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/get-everything-you-need-to-make-valentine-s-day-extra-special-d.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/get-everything-you-need-to-make-valentine-s-day-extra-special-d</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:27.304Z</t>
+  </si>
+  <si>
+    <t>Get everything you need to make Valentine’s Day extra special, delivered by UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/get-everything-you-need-to-make-valentine-s-day-extra-special--d.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/how-one-entrepreneur-got-a-surprise-mentorship-session-with-emma.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/how-one-entrepreneur-got-a-surprise-mentorship-session-with-emma</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:13.809Z</t>
+  </si>
+  <si>
+    <t>How one entrepreneur got a surprise mentorship session with Emma Grede</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/how-one-entrepreneur-got-a-surprise-mentorship-session-with-emma.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/how-ups-powers-small-business-growth.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/how-ups-powers-small-business-growth</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:35.489Z</t>
+  </si>
+  <si>
+    <t>How UPS powers small business growth</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/how-ups-powers-small-business-growth.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/new-shelves-new-customers-same-reliable-shipper.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/new-shelves-new-customers-same-reliable-shipper</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:11:30.812Z</t>
+  </si>
+  <si>
+    <t>New shelves, new customers – same reliable shipper</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/new-shelves--new-customers---same-reliable-shipper.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/our-favorite-moments-delivering-what-matters-in-2025.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/our-favorite-moments-delivering-what-matters-in-2025</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:20.136Z</t>
+  </si>
+  <si>
+    <t>Our favorite moments delivering what matters in 2025</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/our-favorite-moments-delivering-what-matters-in-2025.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/sanmar-and-ups-an-iconic-partnership-delivering-world-class-spe.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/sanmar-and-ups-an-iconic-partnership-delivering-world-class-spe</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:11:37.268Z</t>
+  </si>
+  <si>
+    <t>SanMar and UPS, an iconic partnership delivering world-class speed and reliability</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/sanmar-and-ups--an-iconic-partnership-delivering-world-class-spe.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/seamus-golf-swings-big-through-ups-s-ryder-cup-partnership.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/seamus-golf-swings-big-through-ups-s-ryder-cup-partnership</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:27.256Z</t>
+  </si>
+  <si>
+    <t>Seamus Golf swings big through UPS’s Ryder Cup partnership</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/seamus-golf-swings-big-through-ups-s-ryder-cup-partnership-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/see-how-coco-gauff-emma-grede-and-ups-help-deliver-sweet-succes.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/see-how-coco-gauff-emma-grede-and-ups-help-deliver-sweet-succes</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:33.133Z</t>
+  </si>
+  <si>
+    <t>See how Coco Gauff, Emma Grede and UPS help deliver sweet success for this small business</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/see-how-coco-gauff--emma-grede-and-ups-help-deliver-sweet-succes.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/see-how-ups-delivers-for-one-luxury-bag-brand-crafted-by-african.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/see-how-ups-delivers-for-one-luxury-bag-brand-crafted-by-african</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:38.019Z</t>
+  </si>
+  <si>
+    <t>See how UPS delivers for one luxury bag brand crafted by African artistry</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/see-how-ups-delivers-for-one-luxury-bag-brand-crafted-by-african.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shipping-tips-to-get-the-most-out-of-your-holiday-sales.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shipping-tips-to-get-the-most-out-of-your-holiday-sales</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:42.921Z</t>
+  </si>
+  <si>
+    <t>Shipping tips to get the most out of your holiday sales</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/shipping-tips-to-get-the-most-out-of-your-holiday-sales.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shop-small-ship-smart.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shop-small-ship-smart</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:48:51.026Z</t>
+  </si>
+  <si>
+    <t>Shop small, ship smart: The Small Business Holiday Catalog presented by UPS &amp; American Express</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/shop-small-ship-smart.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shoppers-say-goodbye-to-surprise-tariff-expenses-with-ups-global.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/shoppers-say-goodbye-to-surprise-tariff-expenses-with-ups-global</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:00.221Z</t>
+  </si>
+  <si>
+    <t>Shoppers say goodbye to surprise tariff expenses with UPS Global Checkout</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/shoppers-say-goodbye-to-surprise-tariff-expenses-with-ups-global.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/small-business-big-growth.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/small-business-big-growth</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:07.661Z</t>
+  </si>
+  <si>
+    <t>Small business big growth</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/small-business-big-growth.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/smarter-supply-chains-start-here-with-ups-expertise-leading-th.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/smarter-supply-chains-start-here-with-ups-expertise-leading-th</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:15.178Z</t>
+  </si>
+  <si>
+    <t>Smarter supply chains start here with UPS expertise leading the way</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/smarter-supply-chains-start-here-with-ups-expertise-leading-th.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/subway-takes-creator-kareem-rahma-teams-up-with-ups-for-small.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/subway-takes-creator-kareem-rahma-teams-up-with-ups-for-small</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:05.880Z</t>
+  </si>
+  <si>
+    <t>‘Subway Takes’ creator Kareem Rahma teams up with UPS for small biz love</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/-subway-takes--creator-kareem-rahma-teams-up-with-ups-for-small-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/surf-shop-catches-the-ups-wave-when-previous-carrier-wipes-out.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/surf-shop-catches-the-ups-wave-when-previous-carrier-wipes-out</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:20.006Z</t>
+  </si>
+  <si>
+    <t>Surf shop catches the UPS wave when previous carrier wipes out</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/surf-shop-catches-the-ups-wave-when-previous-carrier-wipes-out.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/the-judges-have-spoken-ups-recognized-for-culture-reputation-a.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/the-judges-have-spoken-ups-recognized-for-culture-reputation-a</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:24.871Z</t>
+  </si>
+  <si>
+    <t>The judges have spoken: UPS recognized for culture, reputation and innovation in 2025</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/the-judges-have-spoken--ups-recognized-for-culture--reputation-a.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/the-ups-store-small-biz-challenge.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/the-ups-store-small-biz-challenge</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:50:08.120Z</t>
+  </si>
+  <si>
+    <t>The UPS Store Small Biz Challenge</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/the-ups-store-small-biz-challenge.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-and-american-express-collaborate-to-make-logistics-and-payme.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-and-american-express-collaborate-to-make-logistics-and-payme</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:33.699Z</t>
+  </si>
+  <si>
+    <t>UPS and American Express collaborate to make logistics and payments easier than ever for businesses</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-and-american-express-collaborate-to-make-logistics-and-payme.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-and-lfc-celebrate-the-unstoppable-spirit-of-liverpool-busi0.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-and-lfc-celebrate-the-unstoppable-spirit-of-liverpool-busi0</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:11:17.027Z</t>
+  </si>
+  <si>
+    <t>UPS and LFC celebrate the Unstoppable Spirit of Liverpool businesses</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-and-lfc-celebrate-the--unstoppable-spirit--of-liverpool-busi0.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-helps-businesses-grow-with-sustainable-shipping-and-easy-ret.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-helps-businesses-grow-with-sustainable-shipping-and-easy-ret</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:39.362Z</t>
+  </si>
+  <si>
+    <t>UPS helps businesses grow with sustainable shipping and easy returns</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-helps-businesses-grow-with-sustainable-shipping-and-easy-ret.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-leads-the-way-in-on-time-delivery-during-the-2025-holiday-se.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-leads-the-way-in-on-time-delivery-during-the-2025-holiday-se</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:47.736Z</t>
+  </si>
+  <si>
+    <t>For 8 years in a row, UPS leads the way in on-time delivery during the holiday season</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-leads-the-way-in-on-time-delivery-during-the-2025-holiday-se.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-partners-with-serial-entrepreneur-emma-grede-and-tennis-grea.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-partners-with-serial-entrepreneur-emma-grede-and-tennis-grea</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:53.453Z</t>
+  </si>
+  <si>
+    <t>UPS partners with serial entrepreneur Emma Grede and tennis great Coco Gauff to unlock small business potential</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-partners-with-serial-entrepreneur-emma-grede-and-tennis-grea.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-tees-up-for-the-2025-ryder-cup.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/ups-tees-up-for-the-2025-ryder-cup</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:49:59.779Z</t>
+  </si>
+  <si>
+    <t>UPS tees up for the 2025 Ryder Cup</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/ups-tees-up-for-the-2025-ryder-cup.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/what-brings-us-together-our-holiday-ups-express-box-delivers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/what-brings-us-together-our-holiday-ups-express-box-delivers</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:47:11.015Z</t>
+  </si>
+  <si>
+    <t>‘What brings us together’ – Our holiday UPS Express Box delivers joy</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/-what-brings-us-together----our-holiday-ups-express-box-delivers.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/woodworking-company-s-export-business-booms-with-help-from-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/customer-first/woodworking-company-s-export-business-booms-with-help-from-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:43.183Z</t>
+  </si>
+  <si>
+    <t>Woodworking company’s export business booms with help from UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/customer-first/woodworking-company-s-export-business-booms-with-help-from-ups.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-things-you-need-to-know-about-the-future-of-healthcare-logisti.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-things-you-need-to-know-about-the-future-of-healthcare-logisti</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:02.574Z</t>
+  </si>
+  <si>
+    <t>3 things you need to know about the future of healthcare logistics</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/3-things-you-need-to-know-about-the-future-of-healthcare-logisti.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-ways-ups-healthcare-delivers-temperature-sensitive-biologics-l.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-ways-ups-healthcare-delivers-temperature-sensitive-biologics-l</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:53.959Z</t>
+  </si>
+  <si>
+    <t>3 ways UPS Healthcare delivers temperature-sensitive biologics like insulin around the world</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/3-ways-ups-healthcare-delivers-temperature-sensitive-biologics-l.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-ways-ups-is-using-smart-tech-today-to-deliver-a-more-sustainab.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/3-ways-ups-is-using-smart-tech-today-to-deliver-a-more-sustainab</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:11.426Z</t>
+  </si>
+  <si>
+    <t>3 ways UPS is using smart tech today to deliver a more sustainable future</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/3-ways-ups-is-using-smart-tech-today-to-deliver-a-more-sustainab.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/5-ways-the-new-ups-velocity-facility-orchestrates.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/5-ways-the-new-ups-velocity-facility-orchestrates</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:34.039Z</t>
+  </si>
+  <si>
+    <t>5 ways the new UPS Velocity facility orchestrates</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/5-ways-the-new-ups-velocity-facility-orchestrates-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/alternative-fuel-technology-showcased-at-expo-2020.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/alternative-fuel-technology-showcased-at-expo-2020</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:23.211Z</t>
+  </si>
+  <si>
+    <t>Alternative fuel technology showcased at Expo 2020 | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/alternative-fuel-technology-showcased-at-expo-2020.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/courage-to-change-how-ups-transformed-to-lead-the-future-of-glo.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/courage-to-change-how-ups-transformed-to-lead-the-future-of-glo</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:56:44.712Z</t>
+  </si>
+  <si>
+    <t>Courage to change: How UPS transformed to lead the future of global commerce</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/courage-to-change--how-ups-transformed-to-lead-the-future-of-glo.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/drone-covid-vaccine-deliveries.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/drone-covid-vaccine-deliveries</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:10.129Z</t>
+  </si>
+  <si>
+    <t>Drone COVID Vaccine Deliveries</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/drone-covid-vaccine-deliveries.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/experience-ups-innovations-at-expo.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/experience-ups-innovations-at-expo</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:03.538Z</t>
+  </si>
+  <si>
+    <t>Experience UPS innovations at Expo</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/experience-ups-innovations-at-expo.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/flightless-birds-land-safely-at-world-expo-in-dubai.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/flightless-birds-land-safely-at-world-expo-in-dubai</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:51.455Z</t>
+  </si>
+  <si>
+    <t>Flightless birds land safely at world expo in Dubai</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/flightless-birds-land-safely-at-world-expo-in-dubai.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/forest-of-the-future.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/forest-of-the-future</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:57.637Z</t>
+  </si>
+  <si>
+    <t>Forest of the Future</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/forest-of-the-future.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/head-of-supply-chain-solutions-at-ups-talks-4-emerging-trends-in.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/head-of-supply-chain-solutions-at-ups-talks-4-emerging-trends-in</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:43.275Z</t>
+  </si>
+  <si>
+    <t>Head of supply chain solutions at UPS talks 4 emerging trends in logistics</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/head-of-supply-chain-solutions-at-ups-talks-4-emerging-trends-in.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/how-ups-is-helping-customers-with-sustainable-logistics.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/how-ups-is-helping-customers-with-sustainable-logistics</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:56:50.934Z</t>
+  </si>
+  <si>
+    <t>How UPS is helping customers with sustainable logistics</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/how-ups-is-helping-customers-with-sustainable-logistics.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/innovation-fuels-global-logistics.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/innovation-fuels-global-logistics</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:32.955Z</t>
+  </si>
+  <si>
+    <t>Innovation fuels global logistics</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/innovation-fuels-global-logistics.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/lessons-from-the-e-bike-journey-of-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/lessons-from-the-e-bike-journey-of-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:43.763Z</t>
+  </si>
+  <si>
+    <t>Lessons from the e-bike journey of UPS | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/lessons-from-the-e-bike-journey-of-ups.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/mobile-training-academy-brings-safety-focused-driver-training-to.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/mobile-training-academy-brings-safety-focused-driver-training-to</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:28.333Z</t>
+  </si>
+  <si>
+    <t>Mobile Training Academy brings safety-focused driver training to UPSers | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/mobile-training-academy-brings-safety-focused-driver-training-to.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-chief-digital-and-technology-officer.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-chief-digital-and-technology-officer</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:38.974Z</t>
+  </si>
+  <si>
+    <t>New Chief Digital and Technology Officer</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/new-chief-digital-and-technology-officer.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-state-of-the-art-ups-facility-opens-in-tacoma-washington.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-state-of-the-art-ups-facility-opens-in-tacoma-washington</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:38.785Z</t>
+  </si>
+  <si>
+    <t>New state-of-the-art UPS facility opens in Tacoma, Washington | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/new-state-of-the-art-ups-facility-opens-in-tacoma-washington.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-ups-electric-vehicles-hit-the-streets-of-europe.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/new-ups-electric-vehicles-hit-the-streets-of-europe</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:11.491Z</t>
+  </si>
+  <si>
+    <t>New UPS electric vehicles hit the streets of Europe</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/new-ups-electric-vehicles-hit-the-streets-of-europe.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/renewable-natural-gas-is-an-important-part-of-ups-strategy-to-in.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/renewable-natural-gas-is-an-important-part-of-ups-strategy-to-in</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:33.646Z</t>
+  </si>
+  <si>
+    <t>Renewable Natural Gas is an important part of UPS strategy to increase alternative fuel consumption | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/renewable-natural-gas-is-an-important-part-of-ups-strategy-to-in.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/top-5-takeaways-from-ups-s-q3-2025-earnings-announcement.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/top-5-takeaways-from-ups-s-q3-2025-earnings-announcement</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:56:39.536Z</t>
+  </si>
+  <si>
+    <t>Top 5 takeaways from UPS’s Q3 2025 earnings announcement</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/top-5-takeaways-from-ups-s-q3-2025-earnings-announcement.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-adds-two-new-cross-docks-in-europe-to-meet-growing-healthcar.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-adds-two-new-cross-docks-in-europe-to-meet-growing-healthcar</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:56:57.423Z</t>
+  </si>
+  <si>
+    <t>UPS adds two new cross-docks in Europe to meet growing healthcare demand</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-adds-two-new-cross-docks-in-europe-to-meet-growing-healthcar.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-and-google-cloud.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-and-google-cloud</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:44.184Z</t>
+  </si>
+  <si>
+    <t>UPS and Google Cloud</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-and-google-cloud.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-and-koda-ship-first-ever-unattended-kidney-on-a-pump.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-and-koda-ship-first-ever-unattended-kidney-on-a-pump</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:05.585Z</t>
+  </si>
+  <si>
+    <t>UPS and KODA ship first-ever unattended kidney on a pump</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-and-koda-ship-first-ever-unattended-kidney-on-a-pump.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-cambridge-cycle-hub-paves-the-way-for-sustainable-city-deliv.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-cambridge-cycle-hub-paves-the-way-for-sustainable-city-deliv</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:28.863Z</t>
+  </si>
+  <si>
+    <t>UPS Cambridge cycle hub paves the way for sustainable city deliveries</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-cambridge-cycle-hub-paves-the-way-for-sustainable-city-deliv.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-healthcare-upgrades-two-facilities-in-italy-with-55-million.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-healthcare-upgrades-two-facilities-in-italy-with-55-million</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:39.055Z</t>
+  </si>
+  <si>
+    <t>UPS Healthcare upgrades two facilities in Italy with €55 million investment</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-healthcare-upgrades-two-facilities-in-italy-with--55-million.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-is-improving-careers-and-access-to-opportunity-with-the-help.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-is-improving-careers-and-access-to-opportunity-with-the-help</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:48.150Z</t>
+  </si>
+  <si>
+    <t>UPS is improving careers and access to opportunity with the help of AI</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-is-improving-careers-and-access-to-opportunity-with-the-help.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-opens-first-dedicated-healthcare-facility-in-ireland.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-opens-first-dedicated-healthcare-facility-in-ireland</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:24.027Z</t>
+  </si>
+  <si>
+    <t>UPS opens first dedicated healthcare facility in Ireland</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-opens-first-dedicated-healthcare-facility-in-ireland.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-opens-new-technology-center-in-chennai-india.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-opens-new-technology-center-in-chennai-india</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:16.727Z</t>
+  </si>
+  <si>
+    <t>UPS opens new technology center in Chennai, India</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-opens-new-technology-center-in-chennai--india.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-recognized-as-one-of-2023-s-most-innovative-companies.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-recognized-as-one-of-2023-s-most-innovative-companies</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:21.798Z</t>
+  </si>
+  <si>
+    <t>UPS recognized as one of 2023’s most innovative companies</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-recognized-as-one-of-2023-s-most-innovative-companies.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-s-deliverydefense-pits-ai-against-criminals.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-s-deliverydefense-pits-ai-against-criminals</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:59.180Z</t>
+  </si>
+  <si>
+    <t>UPS’s DeliveryDefense pits AI against criminals</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-s-deliverydefense-pits-ai-against-criminals.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-takes-center-stage-at-google-cloud-next-24-and-rfid-journal.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-takes-center-stage-at-google-cloud-next-24-and-rfid-journal</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:57:18.423Z</t>
+  </si>
+  <si>
+    <t>UPS takes center stage at Google Cloud Next ‘24 and RFID Journal conferences</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-takes-center-stage-at-google-cloud-next--24-and-rfid-journal.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-teams-up-with-rubicon.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/ups-teams-up-with-rubicon</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:58:27.157Z</t>
+  </si>
+  <si>
+    <t>UPS teams up with Rubicon</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/ups-teams-up-with-rubicon.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/virtual-reality-helping-to-create-safety-for-ups-drivers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/innovation-driven/virtual-reality-helping-to-create-safety-for-ups-drivers</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:59:17.094Z</t>
+  </si>
+  <si>
+    <t>Virtual reality helping to create safety for UPS drivers | About UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/innovation-driven/virtual-reality-helping-to-create-safety-for-ups-drivers.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/40-years-of-service-and-a-lifetime-of-ups-pride.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/40-years-of-service-and-a-lifetime-of-ups-pride</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:18.448Z</t>
+  </si>
+  <si>
+    <t>40 years of service and a lifetime of UPS pride</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/40-years-of-service-and-a-lifetime-of-ups-pride.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/7-things-you-didnt-know-about-ups-and-its-browntail-jets.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/7-things-you-didnt-know-about-ups-and-its-browntail-jets</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:42.113Z</t>
+  </si>
+  <si>
+    <t>7 things you didn’t know about UPS browntails</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/7-things-you-didnt-know-about-ups-and-its-browntail-jets.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/a-letter-to-the-jarvis-family.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/a-letter-to-the-jarvis-family</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:57.987Z</t>
+  </si>
+  <si>
+    <t>A letter to The Jarvis Family</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/a-letter-to-the-jarvis-family.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/a-look-at-the-pioneering-women-who-shaped-ups-history.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/a-look-at-the-pioneering-women-who-shaped-ups-history</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:28.701Z</t>
+  </si>
+  <si>
+    <t>A look at the pioneering women who shaped UPS history</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/a-look-at-the-pioneering-women-who-shaped-ups-history.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/backed-by-ups-one-mother-s-story-of-resilience-and-support.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/backed-by-ups-one-mother-s-story-of-resilience-and-support</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:24.212Z</t>
+  </si>
+  <si>
+    <t>Backed by UPS: One mother’s story of resilience and support</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/backed-by-ups--one-mother-s-story-of-resilience-and-support-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/celebrating-ups-driver-george-lodovico-for-55-years-of-safe-driv.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/celebrating-ups-driver-george-lodovico-for-55-years-of-safe-driv</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:45.301Z</t>
+  </si>
+  <si>
+    <t>Celebrating UPS driver George Lodovico for 55 years of safe driving</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/celebrating-ups-driver-george-lodovico-for-55-years-of-safe-driv.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/cheers-to-118-years-of-ups.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/cheers-to-118-years-of-ups</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:07.041Z</t>
+  </si>
+  <si>
+    <t>Cheers to 118 years of UPS!</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/cheers-to-118-years-of-ups-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-our-customers-hearts-to-ups-words-of-gratitude-for-extrao.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-our-customers-hearts-to-ups-words-of-gratitude-for-extrao</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:06.432Z</t>
+  </si>
+  <si>
+    <t>From our customers’ hearts to UPS: Words of gratitude for extraordinary UPSers</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/from-our-customers--hearts-to-ups--words-of-gratitude-for-extrao.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-the-er-to-ups-one-mom-s-journey-to-flexibility-and-opportu.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-the-er-to-ups-one-mom-s-journey-to-flexibility-and-opportu</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:15.347Z</t>
+  </si>
+  <si>
+    <t>From the ER to UPS: One mom’s journey to flexibility and opportunity</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/from-the-er-to-ups--one-mom-s-journey-to-flexibility-and-opportu.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-the-philippines-to-ireland-we-deliver-the-holidays.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-the-philippines-to-ireland-we-deliver-the-holidays</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:32:04.471Z</t>
+  </si>
+  <si>
+    <t>From the Philippines to Ireland, we deliver the holidays</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/from-the-philippines-to-ireland--we-deliver-the-holidays.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-ups-scholar-to-the-ups-store-owner-and-everything-in-betw.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/from-ups-scholar-to-the-ups-store-owner-and-everything-in-betw</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:19.110Z</t>
+  </si>
+  <si>
+    <t>From UPS scholar to The UPS Store owner … and everything in between</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/from-ups-scholar-to-the-ups-store-owner---and-everything-in-betw.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-driver-mastered-arizona-s-desert-summers.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-driver-mastered-arizona-s-desert-summers</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:39.001Z</t>
+  </si>
+  <si>
+    <t>How one UPS driver mastered Arizona's desert summers</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/how-one-ups-driver-mastered-arizona-s-desert-summers.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-employee-turned-a-job-into-a-thriving-career.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-employee-turned-a-job-into-a-thriving-career</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:38.901Z</t>
+  </si>
+  <si>
+    <t>How one UPS employee turned a job into a thriving career</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/how-one-ups-employee-turned-a-job-into-a-thriving-career.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-leaders-personal-tragedy-ignited-a-passion-for-safet.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-one-ups-leaders-personal-tragedy-ignited-a-passion-for-safet</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:52.403Z</t>
+  </si>
+  <si>
+    <t>How one UPS leaders personal tragedy ignited a passion for safety</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/how-one-ups-leaders-personal-tragedy-ignited-a-passion-for-safet.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-ups-helped-one-employee-find-and-pursue-their-passion.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/how-ups-helped-one-employee-find-and-pursue-their-passion</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:57.712Z</t>
+  </si>
+  <si>
+    <t>How UPS helped one employee find and pursue their passion</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/how-ups-helped-one-employee-find-and-pursue-their-passion.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/iconic-ups-delivery-vehicles-get-new-flair.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/iconic-ups-delivery-vehicles-get-new-flair</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:34.757Z</t>
+  </si>
+  <si>
+    <t>Iconic UPS delivery vehicles get new flair</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/iconic-ups-delivery-vehicles-get-new-flair.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/in-memory-of-ken-jarvis.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/in-memory-of-ken-jarvis</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:03.265Z</t>
+  </si>
+  <si>
+    <t>In memory of Ken Jarvis</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/in-memory-of-ken-jarvis.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/keeping-seasonal-workers-safe.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/keeping-seasonal-workers-safe</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:07.113Z</t>
+  </si>
+  <si>
+    <t>Keeping seasonal workers safe</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/keeping-seasonal-workers-safe.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-cal-murray.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-cal-murray</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:47.107Z</t>
+  </si>
+  <si>
+    <t>Meet Cal Murray</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/meet-cal-murray.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-malina-downey-a-ups-engineer-powering-holiday-operations.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-malina-downey-a-ups-engineer-powering-holiday-operations</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:13.266Z</t>
+  </si>
+  <si>
+    <t>Meet Malina Downey – a UPS engineer powering holiday operations planning</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/meet-malina-downey---a-ups-engineer-powering-holiday-operations-.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-the-ups-ready-team-on-call-to-serve-during-the-busiest-time.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/meet-the-ups-ready-team-on-call-to-serve-during-the-busiest-time</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:01.239Z</t>
+  </si>
+  <si>
+    <t>Meet the UPS Ready Team on-call to serve during the busiest time of year​</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/meet-the-ups-ready-team-on-call-to-serve-during-the-busiest-time.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/national-human-trafficking-prevention-month.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/national-human-trafficking-prevention-month</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:56.274Z</t>
+  </si>
+  <si>
+    <t>National Human Trafficking Prevention Month</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/national-human-trafficking-prevention-month.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/peak-wrap-up.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/peak-wrap-up</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:31:50.416Z</t>
+  </si>
+  <si>
+    <t>Exceptional service starts with exceptional people</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/peak-wrap-up.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/special-olympics-coach-builds-lasting-career-in-a-specialist-rol.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/special-olympics-coach-builds-lasting-career-in-a-specialist-rol</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:23.629Z</t>
+  </si>
+  <si>
+    <t>Special Olympics coach builds lasting career in a specialist role with UPS</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/special-olympics-coach-builds-lasting-career-in-a-specialist-rol.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/sunshine-state-ups-driver-turns-personal-loss-into-heat-safety-l.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/sunshine-state-ups-driver-turns-personal-loss-into-heat-safety-l</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:49.505Z</t>
+  </si>
+  <si>
+    <t>Sunshine State UPS driver turns a loss into a hydration safety lesson</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/sunshine-state-ups-driver-turns-personal-loss-into-heat-safety-l.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-road-to-excellence-ups-drivers-at-the-national-truck-driving.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-road-to-excellence-ups-drivers-at-the-national-truck-driving</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:28.970Z</t>
+  </si>
+  <si>
+    <t>The road to excellence UPS drivers at the National Truck Driving Championships</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/the-road-to-excellence-ups-drivers-at-the-national-truck-driving.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-safest-wheels-on-the-road.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-safest-wheels-on-the-road</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:31.526Z</t>
+  </si>
+  <si>
+    <t>UPS drivers sweep national safety awards, winning in 7 out of 11 regions</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/the-safest-wheels-on-the-road.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-ups-store-bags-fifth-win-at-the-tournament-of-roses.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/the-ups-store-bags-fifth-win-at-the-tournament-of-roses</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:00.502Z</t>
+  </si>
+  <si>
+    <t>The UPS Store bags fifth win at the Tournament of Roses</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/the-ups-store-bags-fifth-win-at-the-tournament-of-roses.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/thirsty-for-safety-how-one-ups-driver-is-making-a-splash.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/thirsty-for-safety-how-one-ups-driver-is-making-a-splash</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:55.786Z</t>
+  </si>
+  <si>
+    <t>Thirsty for safety – how one UPS driver is making a splash</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/thirsty-for-safety---how-one-ups-driver-is-making-a-splash.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-delivers-holiday-shipping-with-flexibility-visibility-and-e.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-delivers-holiday-shipping-with-flexibility-visibility-and-e</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:12.653Z</t>
+  </si>
+  <si>
+    <t>UPS delivers holiday shipping with flexibility, visibility and ease</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/ups-delivers-holiday-shipping-with-flexibility--visibility-and-e.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-driver-joel-reyez-shares-his-tips-to-working-in-the-heat.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-driver-joel-reyez-shares-his-tips-to-working-in-the-heat</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:01:32.561Z</t>
+  </si>
+  <si>
+    <t>UPS driver Joel Reyez shares his tips to working in the heat</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/ups-driver-joel-reyez-shares-his-tips-to-working-in-the-heat.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-driver-retires-after-58-years-and-over-5-million-accident-free-miles.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-driver-retires-after-58-years-and-over-5-million-accident-free-miles</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:26.249Z</t>
+  </si>
+  <si>
+    <t>UPS driver retires after 58 years and over 5 million accident free miles</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/UPS-driver-retires-after-58-years-and-over-5-million-accident-free-miles.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-drivers-shine-at-2025-national-truck-driving-championships.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-drivers-shine-at-2025-national-truck-driving-championships</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:00:48.401Z</t>
+  </si>
+  <si>
+    <t>UPS drivers shine at 2025 National Truck Driving Championships</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/ups-drivers-shine-at-2025-national-truck-driving-championships.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-unveils-prosperous-daruma-express-envelope-design-in-japan.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/ups-unveils-prosperous-daruma-express-envelope-design-in-japan</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:12.027Z</t>
+  </si>
+  <si>
+    <t>UPS unveils Prosperous Daruma Express envelope design in Japan</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/ups-unveils-prosperous-daruma-express-envelope-design-in-japan.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/upss-holiday-hiring-spree.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/upss-holiday-hiring-spree</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:02:22.753Z</t>
+  </si>
+  <si>
+    <t>UPSs holiday hiring spree</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/upss-holiday-hiring-spree.html</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/what-can-brown-noise-do-for-you.report.json</t>
+  </si>
+  <si>
+    <t>us/en/our-stories/people-led/what-can-brown-noise-do-for-you</t>
+  </si>
+  <si>
+    <t>2026-03-10T14:03:07.900Z</t>
+  </si>
+  <si>
+    <t>What can brown noise do for you?</t>
+  </si>
+  <si>
+    <t>https://about.ups.com/us/en/our-stories/people-led/what-can-brown-noise-do-for-you-.html</t>
   </si>
 </sst>
 </file>
@@ -561,19 +2410,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="1" max="6" width="50" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,191 +2444,4463 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
+      <c r="I15" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J16" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" t="s">
+        <v>116</v>
+      </c>
+      <c r="J18" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" t="s">
+        <v>121</v>
+      </c>
+      <c r="J19" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" t="s">
+        <v>127</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" t="s">
+        <v>131</v>
+      </c>
+      <c r="J21" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J23" t="s">
+        <v>142</v>
+      </c>
+      <c r="K23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" t="s">
+        <v>152</v>
+      </c>
+      <c r="K25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" t="s">
+        <v>156</v>
+      </c>
+      <c r="J26" t="s">
+        <v>157</v>
+      </c>
+      <c r="K26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" t="s">
+        <v>161</v>
+      </c>
+      <c r="J27" t="s">
+        <v>162</v>
+      </c>
+      <c r="K27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" t="s">
+        <v>166</v>
+      </c>
+      <c r="J28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" t="s">
+        <v>171</v>
+      </c>
+      <c r="J29" t="s">
+        <v>172</v>
+      </c>
+      <c r="K29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" t="s">
+        <v>181</v>
+      </c>
+      <c r="J31" t="s">
+        <v>182</v>
+      </c>
+      <c r="K31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32" t="s">
+        <v>186</v>
+      </c>
+      <c r="J32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" t="s">
+        <v>191</v>
+      </c>
+      <c r="J33" t="s">
+        <v>192</v>
+      </c>
+      <c r="K33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34" t="s">
+        <v>196</v>
+      </c>
+      <c r="J34" t="s">
+        <v>197</v>
+      </c>
+      <c r="K34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" t="s">
+        <v>201</v>
+      </c>
+      <c r="J35" t="s">
+        <v>202</v>
+      </c>
+      <c r="K35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>204</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36" t="s">
+        <v>206</v>
+      </c>
+      <c r="J36" t="s">
+        <v>207</v>
+      </c>
+      <c r="K36" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37" t="s">
+        <v>211</v>
+      </c>
+      <c r="J37" t="s">
+        <v>212</v>
+      </c>
+      <c r="K37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>215</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" t="s">
+        <v>216</v>
+      </c>
+      <c r="J38" t="s">
+        <v>217</v>
+      </c>
+      <c r="K38" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" t="s">
+        <v>221</v>
+      </c>
+      <c r="J39" t="s">
+        <v>222</v>
+      </c>
+      <c r="K39" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" t="s">
+        <v>226</v>
+      </c>
+      <c r="J40" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>229</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>230</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" t="s">
+        <v>231</v>
+      </c>
+      <c r="J41" t="s">
+        <v>232</v>
+      </c>
+      <c r="K41" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>234</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" t="s">
+        <v>236</v>
+      </c>
+      <c r="J42" t="s">
+        <v>237</v>
+      </c>
+      <c r="K42" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" t="s">
+        <v>241</v>
+      </c>
+      <c r="J43" t="s">
+        <v>242</v>
+      </c>
+      <c r="K43" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>244</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>245</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44" t="s">
+        <v>246</v>
+      </c>
+      <c r="J44" t="s">
+        <v>247</v>
+      </c>
+      <c r="K44" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>249</v>
+      </c>
+      <c r="B45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>250</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" t="s">
+        <v>251</v>
+      </c>
+      <c r="J45" t="s">
+        <v>252</v>
+      </c>
+      <c r="K45" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>254</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>255</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s">
+        <v>52</v>
+      </c>
+      <c r="I46" t="s">
+        <v>256</v>
+      </c>
+      <c r="J46" t="s">
+        <v>257</v>
+      </c>
+      <c r="K46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>260</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s">
+        <v>52</v>
+      </c>
+      <c r="I47" t="s">
+        <v>261</v>
+      </c>
+      <c r="J47" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>264</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>265</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48" t="s">
+        <v>266</v>
+      </c>
+      <c r="J48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K48" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>269</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>270</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>52</v>
+      </c>
+      <c r="I49" t="s">
+        <v>271</v>
+      </c>
+      <c r="J49" t="s">
+        <v>272</v>
+      </c>
+      <c r="K49" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>275</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50" t="s">
+        <v>276</v>
+      </c>
+      <c r="J50" t="s">
+        <v>277</v>
+      </c>
+      <c r="K50" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>279</v>
+      </c>
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>280</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>52</v>
+      </c>
+      <c r="I51" t="s">
+        <v>281</v>
+      </c>
+      <c r="J51" t="s">
+        <v>282</v>
+      </c>
+      <c r="K51" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>284</v>
+      </c>
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>285</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" t="s">
+        <v>286</v>
+      </c>
+      <c r="J52" t="s">
+        <v>287</v>
+      </c>
+      <c r="K52" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>289</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>290</v>
+      </c>
+      <c r="F53" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53" t="s">
+        <v>291</v>
+      </c>
+      <c r="J53" t="s">
+        <v>292</v>
+      </c>
+      <c r="K53" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>295</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54" t="s">
+        <v>296</v>
+      </c>
+      <c r="J54" t="s">
+        <v>297</v>
+      </c>
+      <c r="K54" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>299</v>
+      </c>
+      <c r="B55" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>300</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55" t="s">
+        <v>301</v>
+      </c>
+      <c r="J55" t="s">
+        <v>302</v>
+      </c>
+      <c r="K55" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>305</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56" t="s">
+        <v>306</v>
+      </c>
+      <c r="J56" t="s">
+        <v>307</v>
+      </c>
+      <c r="K56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>309</v>
+      </c>
+      <c r="B57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>310</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="s">
+        <v>52</v>
+      </c>
+      <c r="I57" t="s">
+        <v>311</v>
+      </c>
+      <c r="J57" t="s">
+        <v>312</v>
+      </c>
+      <c r="K57" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>315</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58" t="s">
+        <v>316</v>
+      </c>
+      <c r="J58" t="s">
+        <v>317</v>
+      </c>
+      <c r="K58" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>320</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59" t="s">
+        <v>321</v>
+      </c>
+      <c r="J59" t="s">
+        <v>322</v>
+      </c>
+      <c r="K59" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>324</v>
+      </c>
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>325</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60" t="s">
+        <v>326</v>
+      </c>
+      <c r="J60" t="s">
+        <v>327</v>
+      </c>
+      <c r="K60" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>329</v>
+      </c>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>330</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" t="s">
+        <v>52</v>
+      </c>
+      <c r="I61" t="s">
+        <v>331</v>
+      </c>
+      <c r="J61" t="s">
+        <v>332</v>
+      </c>
+      <c r="K61" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>334</v>
+      </c>
+      <c r="B62" t="s">
+        <v>50</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>335</v>
+      </c>
+      <c r="F62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62" t="s">
+        <v>336</v>
+      </c>
+      <c r="J62" t="s">
+        <v>337</v>
+      </c>
+      <c r="K62" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>339</v>
+      </c>
+      <c r="B63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>340</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>52</v>
+      </c>
+      <c r="I63" t="s">
+        <v>341</v>
+      </c>
+      <c r="J63" t="s">
+        <v>342</v>
+      </c>
+      <c r="K63" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>344</v>
+      </c>
+      <c r="B64" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>345</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64" t="s">
+        <v>346</v>
+      </c>
+      <c r="J64" t="s">
+        <v>347</v>
+      </c>
+      <c r="K64" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>349</v>
+      </c>
+      <c r="B65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>350</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65" t="s">
+        <v>351</v>
+      </c>
+      <c r="J65" t="s">
+        <v>352</v>
+      </c>
+      <c r="K65" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>354</v>
+      </c>
+      <c r="B66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>355</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66" t="s">
+        <v>356</v>
+      </c>
+      <c r="J66" t="s">
+        <v>357</v>
+      </c>
+      <c r="K66" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>359</v>
+      </c>
+      <c r="B67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>360</v>
+      </c>
+      <c r="F67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67" t="s">
+        <v>361</v>
+      </c>
+      <c r="J67" t="s">
+        <v>362</v>
+      </c>
+      <c r="K67" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>365</v>
+      </c>
+      <c r="F68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" t="s">
+        <v>52</v>
+      </c>
+      <c r="I68" t="s">
+        <v>366</v>
+      </c>
+      <c r="J68" t="s">
+        <v>367</v>
+      </c>
+      <c r="K68" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>369</v>
+      </c>
+      <c r="B69" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>370</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s">
+        <v>52</v>
+      </c>
+      <c r="I69" t="s">
+        <v>371</v>
+      </c>
+      <c r="J69" t="s">
+        <v>372</v>
+      </c>
+      <c r="K69" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>374</v>
+      </c>
+      <c r="B70" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>375</v>
+      </c>
+      <c r="F70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" t="s">
+        <v>52</v>
+      </c>
+      <c r="I70" t="s">
+        <v>376</v>
+      </c>
+      <c r="J70" t="s">
+        <v>377</v>
+      </c>
+      <c r="K70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>379</v>
+      </c>
+      <c r="B71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>380</v>
+      </c>
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>52</v>
+      </c>
+      <c r="I71" t="s">
+        <v>381</v>
+      </c>
+      <c r="J71" t="s">
+        <v>382</v>
+      </c>
+      <c r="K71" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>384</v>
+      </c>
+      <c r="B72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>385</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" t="s">
+        <v>52</v>
+      </c>
+      <c r="I72" t="s">
+        <v>386</v>
+      </c>
+      <c r="J72" t="s">
+        <v>387</v>
+      </c>
+      <c r="K72" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>389</v>
+      </c>
+      <c r="B73" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>390</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="s">
+        <v>52</v>
+      </c>
+      <c r="I73" t="s">
+        <v>391</v>
+      </c>
+      <c r="J73" t="s">
+        <v>392</v>
+      </c>
+      <c r="K73" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>394</v>
+      </c>
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>395</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74" t="s">
+        <v>396</v>
+      </c>
+      <c r="J74" t="s">
+        <v>397</v>
+      </c>
+      <c r="K74" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>399</v>
+      </c>
+      <c r="B75" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>400</v>
+      </c>
+      <c r="F75" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75" t="s">
+        <v>401</v>
+      </c>
+      <c r="J75" t="s">
+        <v>402</v>
+      </c>
+      <c r="K75" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>404</v>
+      </c>
+      <c r="B76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>405</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" t="s">
+        <v>52</v>
+      </c>
+      <c r="I76" t="s">
+        <v>406</v>
+      </c>
+      <c r="J76" t="s">
+        <v>407</v>
+      </c>
+      <c r="K76" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>409</v>
+      </c>
+      <c r="B77" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>410</v>
+      </c>
+      <c r="F77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77" t="s">
+        <v>411</v>
+      </c>
+      <c r="J77" t="s">
+        <v>412</v>
+      </c>
+      <c r="K77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>414</v>
+      </c>
+      <c r="B78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>415</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>52</v>
+      </c>
+      <c r="I78" t="s">
+        <v>416</v>
+      </c>
+      <c r="J78" t="s">
+        <v>417</v>
+      </c>
+      <c r="K78" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>419</v>
+      </c>
+      <c r="B79" t="s">
+        <v>50</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>420</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" t="s">
+        <v>52</v>
+      </c>
+      <c r="I79" t="s">
+        <v>421</v>
+      </c>
+      <c r="J79" t="s">
+        <v>422</v>
+      </c>
+      <c r="K79" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>424</v>
+      </c>
+      <c r="B80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>425</v>
+      </c>
+      <c r="F80" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I80" t="s">
+        <v>426</v>
+      </c>
+      <c r="J80" t="s">
+        <v>427</v>
+      </c>
+      <c r="K80" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>429</v>
+      </c>
+      <c r="B81" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>430</v>
+      </c>
+      <c r="F81" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I81" t="s">
+        <v>431</v>
+      </c>
+      <c r="J81" t="s">
+        <v>432</v>
+      </c>
+      <c r="K81" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>434</v>
+      </c>
+      <c r="B82" t="s">
+        <v>50</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>435</v>
+      </c>
+      <c r="F82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J82" t="s">
+        <v>437</v>
+      </c>
+      <c r="K82" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>439</v>
+      </c>
+      <c r="B83" t="s">
+        <v>50</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>440</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="s">
+        <v>52</v>
+      </c>
+      <c r="I83" t="s">
+        <v>441</v>
+      </c>
+      <c r="J83" t="s">
+        <v>442</v>
+      </c>
+      <c r="K83" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>444</v>
+      </c>
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>445</v>
+      </c>
+      <c r="F84" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" t="s">
+        <v>52</v>
+      </c>
+      <c r="I84" t="s">
+        <v>446</v>
+      </c>
+      <c r="J84" t="s">
+        <v>447</v>
+      </c>
+      <c r="K84" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>449</v>
+      </c>
+      <c r="B85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>450</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" t="s">
+        <v>52</v>
+      </c>
+      <c r="I85" t="s">
+        <v>451</v>
+      </c>
+      <c r="J85" t="s">
+        <v>452</v>
+      </c>
+      <c r="K85" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>454</v>
+      </c>
+      <c r="B86" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>455</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" t="s">
+        <v>52</v>
+      </c>
+      <c r="I86" t="s">
+        <v>456</v>
+      </c>
+      <c r="J86" t="s">
+        <v>457</v>
+      </c>
+      <c r="K86" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>459</v>
+      </c>
+      <c r="B87" t="s">
+        <v>50</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>460</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" t="s">
+        <v>52</v>
+      </c>
+      <c r="I87" t="s">
+        <v>461</v>
+      </c>
+      <c r="J87" t="s">
+        <v>462</v>
+      </c>
+      <c r="K87" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>464</v>
+      </c>
+      <c r="B88" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>465</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" t="s">
+        <v>52</v>
+      </c>
+      <c r="I88" t="s">
+        <v>466</v>
+      </c>
+      <c r="J88" t="s">
+        <v>467</v>
+      </c>
+      <c r="K88" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>469</v>
+      </c>
+      <c r="B89" t="s">
+        <v>50</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>470</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89" t="s">
+        <v>471</v>
+      </c>
+      <c r="J89" t="s">
+        <v>472</v>
+      </c>
+      <c r="K89" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>474</v>
+      </c>
+      <c r="B90" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>475</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" t="s">
+        <v>52</v>
+      </c>
+      <c r="I90" t="s">
+        <v>476</v>
+      </c>
+      <c r="J90" t="s">
+        <v>477</v>
+      </c>
+      <c r="K90" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>479</v>
+      </c>
+      <c r="B91" t="s">
+        <v>50</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>480</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91" t="s">
+        <v>481</v>
+      </c>
+      <c r="J91" t="s">
+        <v>482</v>
+      </c>
+      <c r="K91" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>484</v>
+      </c>
+      <c r="B92" t="s">
+        <v>50</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>485</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" t="s">
+        <v>52</v>
+      </c>
+      <c r="I92" t="s">
+        <v>486</v>
+      </c>
+      <c r="J92" t="s">
+        <v>487</v>
+      </c>
+      <c r="K92" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>489</v>
+      </c>
+      <c r="B93" t="s">
+        <v>50</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>490</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" t="s">
+        <v>16</v>
+      </c>
+      <c r="H93" t="s">
+        <v>52</v>
+      </c>
+      <c r="I93" t="s">
+        <v>491</v>
+      </c>
+      <c r="J93" t="s">
+        <v>492</v>
+      </c>
+      <c r="K93" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>494</v>
+      </c>
+      <c r="B94" t="s">
+        <v>50</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>495</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" t="s">
+        <v>52</v>
+      </c>
+      <c r="I94" t="s">
+        <v>496</v>
+      </c>
+      <c r="J94" t="s">
+        <v>497</v>
+      </c>
+      <c r="K94" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>499</v>
+      </c>
+      <c r="B95" t="s">
+        <v>50</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>500</v>
+      </c>
+      <c r="F95" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95" t="s">
+        <v>501</v>
+      </c>
+      <c r="J95" t="s">
+        <v>502</v>
+      </c>
+      <c r="K95" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>504</v>
+      </c>
+      <c r="B96" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>505</v>
+      </c>
+      <c r="F96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96" t="s">
+        <v>506</v>
+      </c>
+      <c r="J96" t="s">
+        <v>507</v>
+      </c>
+      <c r="K96" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>509</v>
+      </c>
+      <c r="B97" t="s">
+        <v>50</v>
+      </c>
+      <c r="C97" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
+        <v>510</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" t="s">
+        <v>52</v>
+      </c>
+      <c r="I97" t="s">
+        <v>511</v>
+      </c>
+      <c r="J97" t="s">
+        <v>512</v>
+      </c>
+      <c r="K97" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>514</v>
+      </c>
+      <c r="B98" t="s">
+        <v>50</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="s">
+        <v>515</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" t="s">
+        <v>52</v>
+      </c>
+      <c r="I98" t="s">
+        <v>516</v>
+      </c>
+      <c r="J98" t="s">
+        <v>517</v>
+      </c>
+      <c r="K98" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>519</v>
+      </c>
+      <c r="B99" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
+        <v>520</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" t="s">
+        <v>52</v>
+      </c>
+      <c r="I99" t="s">
+        <v>521</v>
+      </c>
+      <c r="J99" t="s">
+        <v>522</v>
+      </c>
+      <c r="K99" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>524</v>
+      </c>
+      <c r="B100" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>525</v>
+      </c>
+      <c r="F100" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" t="s">
+        <v>52</v>
+      </c>
+      <c r="I100" t="s">
+        <v>526</v>
+      </c>
+      <c r="J100" t="s">
+        <v>527</v>
+      </c>
+      <c r="K100" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>529</v>
+      </c>
+      <c r="B101" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>530</v>
+      </c>
+      <c r="F101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" t="s">
+        <v>52</v>
+      </c>
+      <c r="I101" t="s">
+        <v>531</v>
+      </c>
+      <c r="J101" t="s">
+        <v>532</v>
+      </c>
+      <c r="K101" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>534</v>
+      </c>
+      <c r="B102" t="s">
+        <v>50</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" t="s">
+        <v>535</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" t="s">
+        <v>52</v>
+      </c>
+      <c r="I102" t="s">
+        <v>536</v>
+      </c>
+      <c r="J102" t="s">
+        <v>537</v>
+      </c>
+      <c r="K102" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>539</v>
+      </c>
+      <c r="B103" t="s">
+        <v>50</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>540</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" t="s">
+        <v>52</v>
+      </c>
+      <c r="I103" t="s">
+        <v>541</v>
+      </c>
+      <c r="J103" t="s">
+        <v>542</v>
+      </c>
+      <c r="K103" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>544</v>
+      </c>
+      <c r="B104" t="s">
+        <v>50</v>
+      </c>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>545</v>
+      </c>
+      <c r="F104" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" t="s">
+        <v>52</v>
+      </c>
+      <c r="I104" t="s">
+        <v>546</v>
+      </c>
+      <c r="J104" t="s">
+        <v>547</v>
+      </c>
+      <c r="K104" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>549</v>
+      </c>
+      <c r="B105" t="s">
+        <v>50</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>550</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" t="s">
+        <v>52</v>
+      </c>
+      <c r="I105" t="s">
+        <v>551</v>
+      </c>
+      <c r="J105" t="s">
+        <v>552</v>
+      </c>
+      <c r="K105" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>554</v>
+      </c>
+      <c r="B106" t="s">
+        <v>50</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>555</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" t="s">
+        <v>52</v>
+      </c>
+      <c r="I106" t="s">
+        <v>556</v>
+      </c>
+      <c r="J106" t="s">
+        <v>557</v>
+      </c>
+      <c r="K106" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>559</v>
+      </c>
+      <c r="B107" t="s">
+        <v>50</v>
+      </c>
+      <c r="C107" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>560</v>
+      </c>
+      <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107" t="s">
+        <v>52</v>
+      </c>
+      <c r="I107" t="s">
+        <v>561</v>
+      </c>
+      <c r="J107" t="s">
+        <v>562</v>
+      </c>
+      <c r="K107" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>564</v>
+      </c>
+      <c r="B108" t="s">
+        <v>50</v>
+      </c>
+      <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>565</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" t="s">
+        <v>52</v>
+      </c>
+      <c r="I108" t="s">
+        <v>566</v>
+      </c>
+      <c r="J108" t="s">
+        <v>567</v>
+      </c>
+      <c r="K108" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>569</v>
+      </c>
+      <c r="B109" t="s">
+        <v>50</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" t="s">
+        <v>570</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" t="s">
+        <v>52</v>
+      </c>
+      <c r="I109" t="s">
+        <v>571</v>
+      </c>
+      <c r="J109" t="s">
+        <v>572</v>
+      </c>
+      <c r="K109" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>574</v>
+      </c>
+      <c r="B110" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>575</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" t="s">
+        <v>52</v>
+      </c>
+      <c r="I110" t="s">
+        <v>576</v>
+      </c>
+      <c r="J110" t="s">
+        <v>577</v>
+      </c>
+      <c r="K110" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>579</v>
+      </c>
+      <c r="B111" t="s">
+        <v>50</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>580</v>
+      </c>
+      <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" t="s">
+        <v>52</v>
+      </c>
+      <c r="I111" t="s">
+        <v>581</v>
+      </c>
+      <c r="J111" t="s">
+        <v>582</v>
+      </c>
+      <c r="K111" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>584</v>
+      </c>
+      <c r="B112" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>585</v>
+      </c>
+      <c r="F112" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" t="s">
+        <v>52</v>
+      </c>
+      <c r="I112" t="s">
+        <v>586</v>
+      </c>
+      <c r="J112" t="s">
+        <v>587</v>
+      </c>
+      <c r="K112" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>589</v>
+      </c>
+      <c r="B113" t="s">
+        <v>50</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>590</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" t="s">
+        <v>52</v>
+      </c>
+      <c r="I113" t="s">
+        <v>591</v>
+      </c>
+      <c r="J113" t="s">
+        <v>592</v>
+      </c>
+      <c r="K113" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>594</v>
+      </c>
+      <c r="B114" t="s">
+        <v>50</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>595</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="s">
+        <v>52</v>
+      </c>
+      <c r="I114" t="s">
+        <v>596</v>
+      </c>
+      <c r="J114" t="s">
+        <v>597</v>
+      </c>
+      <c r="K114" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>599</v>
+      </c>
+      <c r="B115" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
+        <v>600</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115" t="s">
+        <v>52</v>
+      </c>
+      <c r="I115" t="s">
+        <v>601</v>
+      </c>
+      <c r="J115" t="s">
+        <v>602</v>
+      </c>
+      <c r="K115" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>604</v>
+      </c>
+      <c r="B116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>605</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" t="s">
+        <v>52</v>
+      </c>
+      <c r="I116" t="s">
+        <v>606</v>
+      </c>
+      <c r="J116" t="s">
+        <v>607</v>
+      </c>
+      <c r="K116" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>609</v>
+      </c>
+      <c r="B117" t="s">
+        <v>50</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>610</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" t="s">
+        <v>52</v>
+      </c>
+      <c r="I117" t="s">
+        <v>611</v>
+      </c>
+      <c r="J117" t="s">
+        <v>612</v>
+      </c>
+      <c r="K117" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>614</v>
+      </c>
+      <c r="B118" t="s">
+        <v>50</v>
+      </c>
+      <c r="C118" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
+        <v>615</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118" t="s">
+        <v>52</v>
+      </c>
+      <c r="I118" t="s">
+        <v>616</v>
+      </c>
+      <c r="J118" t="s">
+        <v>617</v>
+      </c>
+      <c r="K118" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>619</v>
+      </c>
+      <c r="B119" t="s">
+        <v>50</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
+        <v>620</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119" t="s">
+        <v>52</v>
+      </c>
+      <c r="I119" t="s">
+        <v>621</v>
+      </c>
+      <c r="J119" t="s">
+        <v>622</v>
+      </c>
+      <c r="K119" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>624</v>
+      </c>
+      <c r="B120" t="s">
+        <v>50</v>
+      </c>
+      <c r="C120" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" t="s">
+        <v>625</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" t="s">
+        <v>16</v>
+      </c>
+      <c r="H120" t="s">
+        <v>52</v>
+      </c>
+      <c r="I120" t="s">
+        <v>626</v>
+      </c>
+      <c r="J120" t="s">
+        <v>627</v>
+      </c>
+      <c r="K120" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>629</v>
+      </c>
+      <c r="B121" t="s">
+        <v>50</v>
+      </c>
+      <c r="C121" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>630</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" t="s">
+        <v>52</v>
+      </c>
+      <c r="I121" t="s">
+        <v>631</v>
+      </c>
+      <c r="J121" t="s">
+        <v>632</v>
+      </c>
+      <c r="K121" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>634</v>
+      </c>
+      <c r="B122" t="s">
+        <v>50</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" t="s">
+        <v>635</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" t="s">
+        <v>52</v>
+      </c>
+      <c r="I122" t="s">
+        <v>636</v>
+      </c>
+      <c r="J122" t="s">
+        <v>637</v>
+      </c>
+      <c r="K122" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>639</v>
+      </c>
+      <c r="B123" t="s">
+        <v>50</v>
+      </c>
+      <c r="C123" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>640</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" t="s">
+        <v>52</v>
+      </c>
+      <c r="I123" t="s">
+        <v>641</v>
+      </c>
+      <c r="J123" t="s">
+        <v>642</v>
+      </c>
+      <c r="K123" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>644</v>
+      </c>
+      <c r="B124" t="s">
+        <v>50</v>
+      </c>
+      <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>645</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" t="s">
+        <v>16</v>
+      </c>
+      <c r="H124" t="s">
+        <v>52</v>
+      </c>
+      <c r="I124" t="s">
+        <v>646</v>
+      </c>
+      <c r="J124" t="s">
+        <v>647</v>
+      </c>
+      <c r="K124" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>649</v>
+      </c>
+      <c r="B125" t="s">
+        <v>50</v>
+      </c>
+      <c r="C125" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="s">
+        <v>650</v>
+      </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" t="s">
+        <v>52</v>
+      </c>
+      <c r="I125" t="s">
+        <v>651</v>
+      </c>
+      <c r="J125" t="s">
+        <v>652</v>
+      </c>
+      <c r="K125" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>654</v>
+      </c>
+      <c r="B126" t="s">
+        <v>50</v>
+      </c>
+      <c r="C126" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>655</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126" t="s">
+        <v>52</v>
+      </c>
+      <c r="I126" t="s">
+        <v>656</v>
+      </c>
+      <c r="J126" t="s">
+        <v>657</v>
+      </c>
+      <c r="K126" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>659</v>
+      </c>
+      <c r="B127" t="s">
+        <v>50</v>
+      </c>
+      <c r="C127" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>660</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" t="s">
+        <v>52</v>
+      </c>
+      <c r="I127" t="s">
+        <v>661</v>
+      </c>
+      <c r="J127" t="s">
+        <v>662</v>
+      </c>
+      <c r="K127" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>664</v>
+      </c>
+      <c r="B128" t="s">
+        <v>50</v>
+      </c>
+      <c r="C128" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" t="s">
+        <v>665</v>
+      </c>
+      <c r="F128" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128" t="s">
+        <v>52</v>
+      </c>
+      <c r="I128" t="s">
+        <v>666</v>
+      </c>
+      <c r="J128" t="s">
+        <v>667</v>
+      </c>
+      <c r="K128" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
